--- a/models/results_for_slides.xlsx
+++ b/models/results_for_slides.xlsx
@@ -461,81 +461,81 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>baseline_mean</t>
+          <t>elasticnet</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0634987652099802</v>
+        <v>0.06330727122051803</v>
       </c>
       <c r="C2" t="n">
-        <v>0.0528668239999761</v>
+        <v>0.05280280309155961</v>
       </c>
       <c r="D2" t="n">
-        <v>-0.2864218609185718</v>
+        <v>-0.2786746045705699</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>baseline_lag1</t>
+          <t>baseline_mean</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.06615911947656748</v>
+        <v>0.0634987652099802</v>
       </c>
       <c r="C3" t="n">
-        <v>0.05419978126475698</v>
+        <v>0.0528668239999761</v>
       </c>
       <c r="D3" t="n">
-        <v>-0.3964721675120177</v>
+        <v>-0.2864218609185718</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>baseline_lag1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.0786771166659747</v>
+        <v>0.06615911947656748</v>
       </c>
       <c r="C4" t="n">
-        <v>0.0651765782934234</v>
+        <v>0.05419978126475698</v>
       </c>
       <c r="D4" t="n">
-        <v>-0.9749209767795524</v>
+        <v>-0.3964721675120177</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>lasso</t>
+          <t>gbr</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>0.0829218274185004</v>
+        <v>0.07740978545257177</v>
       </c>
       <c r="C5" t="n">
-        <v>0.0662405313153909</v>
+        <v>0.06308695846548222</v>
       </c>
       <c r="D5" t="n">
-        <v>-1.193767409358066</v>
+        <v>-0.9118093399487666</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>gbr</t>
+          <t>lasso</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.08720573230928669</v>
+        <v>0.0806453816537093</v>
       </c>
       <c r="C6" t="n">
-        <v>0.07419692673310727</v>
+        <v>0.06326765149223694</v>
       </c>
       <c r="D6" t="n">
-        <v>-1.426291173248283</v>
+        <v>-1.074970155159041</v>
       </c>
     </row>
     <row r="7">
@@ -545,13 +545,13 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>0.1462992566552595</v>
+        <v>0.1015086361639786</v>
       </c>
       <c r="C7" t="n">
-        <v>0.1051103066774872</v>
+        <v>0.07307916877242907</v>
       </c>
       <c r="D7" t="n">
-        <v>-5.828685169186918</v>
+        <v>-2.287447583584253</v>
       </c>
     </row>
   </sheetData>
@@ -621,13 +621,13 @@
         <v>43830</v>
       </c>
       <c r="E2" t="n">
-        <v>0.2364884806651377</v>
+        <v>0.1620305592944967</v>
       </c>
       <c r="F2" t="n">
-        <v>0.2143996967656548</v>
+        <v>0.1362972766022004</v>
       </c>
       <c r="G2" t="n">
-        <v>-30.48212906601244</v>
+        <v>-13.77875926825555</v>
       </c>
     </row>
     <row r="3">
@@ -646,13 +646,13 @@
         <v>44651</v>
       </c>
       <c r="E3" t="n">
-        <v>0.05416487152045399</v>
+        <v>0.04285472950525197</v>
       </c>
       <c r="F3" t="n">
-        <v>0.04560082040687244</v>
+        <v>0.03963497242930783</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.7860417478330932</v>
+        <v>-0.1180305941016033</v>
       </c>
     </row>
     <row r="4">
@@ -671,13 +671,13 @@
         <v>45473</v>
       </c>
       <c r="E4" t="n">
-        <v>0.07314220874100007</v>
+        <v>0.05311854347925255</v>
       </c>
       <c r="F4" t="n">
-        <v>0.05533040285993448</v>
+        <v>0.043305257285779</v>
       </c>
       <c r="G4" t="n">
-        <v>-1.474973365406541</v>
+        <v>-0.305349189392115</v>
       </c>
     </row>
     <row r="5">
@@ -696,13 +696,13 @@
         <v>43830</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1182303824111629</v>
+        <v>0.1215141271314605</v>
       </c>
       <c r="F5" t="n">
-        <v>0.1102406797093983</v>
+        <v>0.1082171147171684</v>
       </c>
       <c r="G5" t="n">
-        <v>-6.868687562254529</v>
+        <v>-7.31184921190412</v>
       </c>
     </row>
     <row r="6">
@@ -721,13 +721,13 @@
         <v>44651</v>
       </c>
       <c r="E6" t="n">
-        <v>0.05302349539297027</v>
+        <v>0.04398491785217298</v>
       </c>
       <c r="F6" t="n">
-        <v>0.0417990803759313</v>
+        <v>0.03604813931426722</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.7115629581686562</v>
+        <v>-0.1777788245904259</v>
       </c>
     </row>
     <row r="7">
@@ -746,13 +746,13 @@
         <v>45473</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0619529983010713</v>
+        <v>0.05301581514259823</v>
       </c>
       <c r="F7" t="n">
-        <v>0.04668183386084308</v>
+        <v>0.04553770044527522</v>
       </c>
       <c r="G7" t="n">
-        <v>-0.775656872742035</v>
+        <v>-0.3003051247500148</v>
       </c>
     </row>
     <row r="8">
@@ -771,13 +771,13 @@
         <v>43830</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1081675670365961</v>
+        <v>0.1147384016753198</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09933627450430298</v>
+        <v>0.1067140963706275</v>
       </c>
       <c r="G8" t="n">
-        <v>-5.586250364685106</v>
+        <v>-6.410742179119791</v>
       </c>
     </row>
     <row r="9">
@@ -796,13 +796,13 @@
         <v>44651</v>
       </c>
       <c r="E9" t="n">
-        <v>0.07539213465446257</v>
+        <v>0.04689973421795179</v>
       </c>
       <c r="F9" t="n">
-        <v>0.06264633741922337</v>
+        <v>0.04131386883023386</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.460256169423689</v>
+        <v>-0.339050433873803</v>
       </c>
     </row>
     <row r="10">
@@ -821,19 +821,19 @@
         <v>45473</v>
       </c>
       <c r="E10" t="n">
-        <v>0.0736907234081996</v>
+        <v>0.05111104345166546</v>
       </c>
       <c r="F10" t="n">
-        <v>0.06060816827579547</v>
+        <v>0.0412329101955853</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.512233644543515</v>
+        <v>-0.208547939664157</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>elasticnet</t>
         </is>
       </c>
       <c r="B11" t="n">
@@ -846,19 +846,19 @@
         <v>43830</v>
       </c>
       <c r="E11" t="n">
-        <v>0.1026466395242242</v>
+        <v>0.07868541903020818</v>
       </c>
       <c r="F11" t="n">
-        <v>0.09419883466822716</v>
+        <v>0.07149784189092098</v>
       </c>
       <c r="G11" t="n">
-        <v>-4.93107730374556</v>
+        <v>-2.485239573742289</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>elasticnet</t>
         </is>
       </c>
       <c r="B12" t="n">
@@ -871,19 +871,19 @@
         <v>44651</v>
       </c>
       <c r="E12" t="n">
-        <v>0.06394962846395835</v>
+        <v>0.05013270417381763</v>
       </c>
       <c r="F12" t="n">
-        <v>0.05026303131785545</v>
+        <v>0.04075932949909414</v>
       </c>
       <c r="G12" t="n">
-        <v>-1.489615176347239</v>
+        <v>-0.5300246716462684</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>rf</t>
+          <t>elasticnet</t>
         </is>
       </c>
       <c r="B13" t="n">
@@ -896,13 +896,13 @@
         <v>45473</v>
       </c>
       <c r="E13" t="n">
-        <v>0.06280428706959294</v>
+        <v>0.05760858071872396</v>
       </c>
       <c r="F13" t="n">
-        <v>0.05106786889418755</v>
+        <v>0.04615123788466372</v>
       </c>
       <c r="G13" t="n">
-        <v>-0.8247903167945376</v>
+        <v>-0.5353547582379157</v>
       </c>
     </row>
   </sheetData>
@@ -916,7 +916,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B12"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -934,81 +934,111 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>excess_ret_lag1</t>
+          <t>cpi_yoy_lag1</t>
         </is>
       </c>
       <c r="B2" t="n">
-        <v>0.0008489089946170586</v>
+        <v>0</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>q_cos</t>
+          <t>gdp_yoy_lag1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.0001866813447933599</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>repo_chg_bps</t>
+          <t>repo_chg_bps_lag1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>-0.0001169142287545125</v>
+        <v>0</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>gdp_yoy</t>
+          <t>rain_anom_lag1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.0001392605262708163</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>q_sin</t>
+          <t>cpi_yoy_diff</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>-0.0001875161172763328</v>
+        <v>0</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>excess_ret_ma4</t>
+          <t>gdp_yoy_diff</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.0004961621440326883</v>
+        <v>0</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>rain_anom</t>
+          <t>rain_anom_diff</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>-0.0006107789650617222</v>
+        <v>0</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>cpi_yoy</t>
+          <t>excess_ret_lag1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>-0.002041793084359372</v>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>excess_ret_ma4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>q_sin</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>q_cos</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -1022,51 +1052,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J10"/>
+  <dimension ref="A1:M13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>cpi_yoy</t>
+          <t>cpi_yoy_lag1</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>gdp_yoy</t>
+          <t>gdp_yoy_lag1</t>
         </is>
       </c>
       <c r="D1" s="1" t="inlineStr">
         <is>
-          <t>repo_chg_bps</t>
+          <t>repo_chg_bps_lag1</t>
         </is>
       </c>
       <c r="E1" s="1" t="inlineStr">
         <is>
-          <t>rain_anom</t>
+          <t>rain_anom_lag1</t>
         </is>
       </c>
       <c r="F1" s="1" t="inlineStr">
         <is>
+          <t>cpi_yoy_diff</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>gdp_yoy_diff</t>
+        </is>
+      </c>
+      <c r="H1" s="1" t="inlineStr">
+        <is>
+          <t>rain_anom_diff</t>
+        </is>
+      </c>
+      <c r="I1" s="1" t="inlineStr">
+        <is>
+          <t>excess_ret_lag1</t>
+        </is>
+      </c>
+      <c r="J1" s="1" t="inlineStr">
+        <is>
+          <t>excess_ret_ma4</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
           <t>q_sin</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="L1" s="1" t="inlineStr">
         <is>
           <t>q_cos</t>
         </is>
       </c>
-      <c r="H1" s="1" t="inlineStr">
-        <is>
-          <t>excess_ret_lag1</t>
-        </is>
-      </c>
-      <c r="I1" s="1" t="inlineStr">
-        <is>
-          <t>excess_ret_ma4</t>
-        </is>
-      </c>
-      <c r="J1" s="1" t="inlineStr">
+      <c r="M1" s="1" t="inlineStr">
         <is>
           <t>target_next</t>
         </is>
@@ -1075,306 +1120,516 @@
     <row r="2">
       <c r="A2" s="1" t="inlineStr">
         <is>
-          <t>cpi_yoy</t>
+          <t>cpi_yoy_lag1</t>
         </is>
       </c>
       <c r="B2" t="n">
         <v>1</v>
       </c>
       <c r="C2" t="n">
-        <v>0.2547234868325111</v>
+        <v>0.2575033195371303</v>
       </c>
       <c r="D2" t="n">
-        <v>0.334835126692435</v>
+        <v>0.3319900272062652</v>
       </c>
       <c r="E2" t="n">
-        <v>-0.1927523356833859</v>
+        <v>-0.2090965296142613</v>
       </c>
       <c r="F2" t="n">
-        <v>0.01216338658884695</v>
+        <v>-0.4176437376370425</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.02142265742278255</v>
+        <v>0.143790239289536</v>
       </c>
       <c r="H2" t="n">
-        <v>0.1532055643033149</v>
+        <v>0.3365896121350026</v>
       </c>
       <c r="I2" t="n">
-        <v>0.1703261480751888</v>
+        <v>0.1847847358116447</v>
       </c>
       <c r="J2" t="n">
-        <v>0.2346040255901717</v>
+        <v>0.3021726934745547</v>
+      </c>
+      <c r="K2" t="n">
+        <v>-0.02470194232949214</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.03437636345743597</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0.3948998820423437</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="1" t="inlineStr">
         <is>
-          <t>gdp_yoy</t>
+          <t>gdp_yoy_lag1</t>
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.2547234868325111</v>
+        <v>0.2575033195371303</v>
       </c>
       <c r="C3" t="n">
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>0.2975153635248759</v>
+        <v>0.2975617274167514</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1757684209926281</v>
+        <v>0.1745612110670851</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.01612141250705025</v>
+        <v>-0.3919612936477426</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.02690509370637225</v>
+        <v>-0.5473828382707028</v>
       </c>
       <c r="H3" t="n">
-        <v>0.3703352929277454</v>
+        <v>-0.06017636381923028</v>
       </c>
       <c r="I3" t="n">
-        <v>0.4359578463779868</v>
+        <v>0.3021276861164438</v>
       </c>
       <c r="J3" t="n">
-        <v>0.07515953066893369</v>
+        <v>0.450808350597353</v>
+      </c>
+      <c r="K3" t="n">
+        <v>-0.0201054997737577</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.02425357286211847</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0.196796361364989</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="1" t="inlineStr">
         <is>
-          <t>repo_chg_bps</t>
+          <t>repo_chg_bps_lag1</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>0.334835126692435</v>
+        <v>0.3319900272062652</v>
       </c>
       <c r="C4" t="n">
-        <v>0.2975153635248759</v>
+        <v>0.2975617274167514</v>
       </c>
       <c r="D4" t="n">
         <v>1</v>
       </c>
       <c r="E4" t="n">
-        <v>0.137229883225497</v>
+        <v>0.1368078006551225</v>
       </c>
       <c r="F4" t="n">
-        <v>-0.155657311668854</v>
+        <v>-0.3143281520559367</v>
       </c>
       <c r="G4" t="n">
-        <v>0.01113546019996191</v>
+        <v>-0.04140296039047354</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.07284246716696963</v>
+        <v>-0.1065468565465815</v>
       </c>
       <c r="I4" t="n">
-        <v>0.08599256096948529</v>
+        <v>0.08078313910631604</v>
       </c>
       <c r="J4" t="n">
-        <v>-0.07426022590193031</v>
+        <v>0.01342354534587349</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.01582955711886647</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.1558964427994675</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0.01994689434184055</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="1" t="inlineStr">
         <is>
-          <t>rain_anom</t>
+          <t>rain_anom_lag1</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>-0.1927523356833859</v>
+        <v>-0.2090965296142613</v>
       </c>
       <c r="C5" t="n">
-        <v>0.1757684209926281</v>
+        <v>0.1745612110670851</v>
       </c>
       <c r="D5" t="n">
-        <v>0.137229883225497</v>
+        <v>0.1368078006551225</v>
       </c>
       <c r="E5" t="n">
         <v>1</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.02229859132677753</v>
+        <v>-0.1895416551052257</v>
       </c>
       <c r="G5" t="n">
-        <v>1.725108938343355e-17</v>
+        <v>-0.04120494326574464</v>
       </c>
       <c r="H5" t="n">
-        <v>0.231673874553956</v>
+        <v>-0.3839175651166943</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2180586528975218</v>
+        <v>0.2052710871353749</v>
       </c>
       <c r="J5" t="n">
-        <v>0.03792246922209327</v>
+        <v>0.1796617745004749</v>
+      </c>
+      <c r="K5" t="n">
+        <v>-0.01911990496177688</v>
+      </c>
+      <c r="L5" t="n">
+        <v>6.892103818890888e-18</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0.2463432077786752</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="1" t="inlineStr">
         <is>
-          <t>q_sin</t>
+          <t>cpi_yoy_diff</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>0.01216338658884695</v>
+        <v>-0.4176437376370425</v>
       </c>
       <c r="C6" t="n">
-        <v>-0.01612141250705025</v>
+        <v>-0.3919612936477426</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.155657311668854</v>
+        <v>-0.3143281520559367</v>
       </c>
       <c r="E6" t="n">
-        <v>-0.02229859132677753</v>
+        <v>-0.1895416551052257</v>
       </c>
       <c r="F6" t="n">
         <v>1</v>
       </c>
       <c r="G6" t="n">
-        <v>-6.464996920408965e-17</v>
+        <v>0.1650110371336946</v>
       </c>
       <c r="H6" t="n">
-        <v>0.09197935394621638</v>
+        <v>-0.1477147190019857</v>
       </c>
       <c r="I6" t="n">
-        <v>0.03653245921552385</v>
+        <v>-0.04439534682431138</v>
       </c>
       <c r="J6" t="n">
-        <v>-0.006348934801478068</v>
+        <v>-0.1729257686298825</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.0467679596777702</v>
+      </c>
+      <c r="L6" t="n">
+        <v>-0.07070777332733652</v>
+      </c>
+      <c r="M6" t="n">
+        <v>-0.2109679840601592</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="1" t="inlineStr">
         <is>
-          <t>q_cos</t>
+          <t>gdp_yoy_diff</t>
         </is>
       </c>
       <c r="B7" t="n">
-        <v>-0.02142265742278255</v>
+        <v>0.143790239289536</v>
       </c>
       <c r="C7" t="n">
-        <v>-0.02690509370637225</v>
+        <v>-0.5473828382707028</v>
       </c>
       <c r="D7" t="n">
-        <v>0.01113546019996191</v>
+        <v>-0.04140296039047354</v>
       </c>
       <c r="E7" t="n">
-        <v>1.725108938343355e-17</v>
+        <v>-0.04120494326574464</v>
       </c>
       <c r="F7" t="n">
-        <v>-6.464996920408965e-17</v>
+        <v>0.1650110371336946</v>
       </c>
       <c r="G7" t="n">
         <v>1</v>
       </c>
       <c r="H7" t="n">
-        <v>0.1613474860758392</v>
+        <v>0.110018954829264</v>
       </c>
       <c r="I7" t="n">
-        <v>0.01733035863151898</v>
+        <v>0.06225851214029582</v>
       </c>
       <c r="J7" t="n">
-        <v>-0.1750732526460696</v>
+        <v>-0.01364561355412725</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.003643198422219131</v>
+      </c>
+      <c r="L7" t="n">
+        <v>-0.04674047515208119</v>
+      </c>
+      <c r="M7" t="n">
+        <v>-0.1111563078875181</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="1" t="inlineStr">
         <is>
-          <t>excess_ret_lag1</t>
+          <t>rain_anom_diff</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.1532055643033149</v>
+        <v>0.3365896121350026</v>
       </c>
       <c r="C8" t="n">
-        <v>0.3703352929277454</v>
+        <v>-0.06017636381923028</v>
       </c>
       <c r="D8" t="n">
-        <v>-0.07284246716696963</v>
+        <v>-0.1065468565465815</v>
       </c>
       <c r="E8" t="n">
-        <v>0.231673874553956</v>
+        <v>-0.3839175651166943</v>
       </c>
       <c r="F8" t="n">
-        <v>0.09197935394621638</v>
+        <v>-0.1477147190019857</v>
       </c>
       <c r="G8" t="n">
-        <v>0.1613474860758392</v>
+        <v>0.110018954829264</v>
       </c>
       <c r="H8" t="n">
         <v>1</v>
       </c>
       <c r="I8" t="n">
-        <v>0.5343236352218353</v>
+        <v>0.03416211695090017</v>
       </c>
       <c r="J8" t="n">
-        <v>0.01309623784164529</v>
+        <v>0.04986874813225276</v>
+      </c>
+      <c r="K8" t="n">
+        <v>-0.004121679828450572</v>
+      </c>
+      <c r="L8" t="n">
+        <v>-2.869394774092018e-18</v>
+      </c>
+      <c r="M8" t="n">
+        <v>-0.2726196665186457</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="1" t="inlineStr">
         <is>
-          <t>excess_ret_ma4</t>
+          <t>excess_ret_lag1</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.1703261480751888</v>
+        <v>0.1847847358116447</v>
       </c>
       <c r="C9" t="n">
-        <v>0.4359578463779868</v>
+        <v>0.3021276861164438</v>
       </c>
       <c r="D9" t="n">
-        <v>0.08599256096948529</v>
+        <v>0.08078313910631604</v>
       </c>
       <c r="E9" t="n">
-        <v>0.2180586528975218</v>
+        <v>0.2052710871353749</v>
       </c>
       <c r="F9" t="n">
-        <v>0.03653245921552385</v>
+        <v>-0.04439534682431138</v>
       </c>
       <c r="G9" t="n">
-        <v>0.01733035863151898</v>
+        <v>0.06225851214029582</v>
       </c>
       <c r="H9" t="n">
-        <v>0.5343236352218353</v>
+        <v>0.03416211695090017</v>
       </c>
       <c r="I9" t="n">
         <v>1</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2099841321712681</v>
+        <v>0.5343236352218353</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.09197935394621636</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.1613474860758392</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0.01309623784164529</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="1" t="inlineStr">
         <is>
+          <t>excess_ret_ma4</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>0.3021726934745547</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.450808350597353</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.01342354534587349</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0.1796617745004749</v>
+      </c>
+      <c r="F10" t="n">
+        <v>-0.1729257686298825</v>
+      </c>
+      <c r="G10" t="n">
+        <v>-0.01364561355412725</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.04986874813225276</v>
+      </c>
+      <c r="I10" t="n">
+        <v>0.5343236352218353</v>
+      </c>
+      <c r="J10" t="n">
+        <v>1</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.03653245921552385</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.017330358631519</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0.2099841321712681</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="inlineStr">
+        <is>
+          <t>q_sin</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>-0.02470194232949214</v>
+      </c>
+      <c r="C11" t="n">
+        <v>-0.0201054997737577</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.01582955711886647</v>
+      </c>
+      <c r="E11" t="n">
+        <v>-0.01911990496177688</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0.0467679596777702</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.003643198422219131</v>
+      </c>
+      <c r="H11" t="n">
+        <v>-0.004121679828450572</v>
+      </c>
+      <c r="I11" t="n">
+        <v>0.09197935394621636</v>
+      </c>
+      <c r="J11" t="n">
+        <v>0.03653245921552385</v>
+      </c>
+      <c r="K11" t="n">
+        <v>1</v>
+      </c>
+      <c r="L11" t="n">
+        <v>-6.464996920408965e-17</v>
+      </c>
+      <c r="M11" t="n">
+        <v>-0.006348934801478068</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="inlineStr">
+        <is>
+          <t>q_cos</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>0.03437636345743597</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.02425357286211847</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.1558964427994675</v>
+      </c>
+      <c r="E12" t="n">
+        <v>6.892103818890888e-18</v>
+      </c>
+      <c r="F12" t="n">
+        <v>-0.07070777332733652</v>
+      </c>
+      <c r="G12" t="n">
+        <v>-0.04674047515208119</v>
+      </c>
+      <c r="H12" t="n">
+        <v>-2.869394774092018e-18</v>
+      </c>
+      <c r="I12" t="n">
+        <v>0.1613474860758392</v>
+      </c>
+      <c r="J12" t="n">
+        <v>0.017330358631519</v>
+      </c>
+      <c r="K12" t="n">
+        <v>-6.464996920408965e-17</v>
+      </c>
+      <c r="L12" t="n">
+        <v>1</v>
+      </c>
+      <c r="M12" t="n">
+        <v>-0.1750732526460696</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
           <t>target_next</t>
         </is>
       </c>
-      <c r="B10" t="n">
-        <v>0.2346040255901717</v>
-      </c>
-      <c r="C10" t="n">
-        <v>0.07515953066893369</v>
-      </c>
-      <c r="D10" t="n">
-        <v>-0.07426022590193031</v>
-      </c>
-      <c r="E10" t="n">
-        <v>0.03792246922209327</v>
-      </c>
-      <c r="F10" t="n">
+      <c r="B13" t="n">
+        <v>0.3948998820423437</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.196796361364989</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.01994689434184055</v>
+      </c>
+      <c r="E13" t="n">
+        <v>0.2463432077786752</v>
+      </c>
+      <c r="F13" t="n">
+        <v>-0.2109679840601592</v>
+      </c>
+      <c r="G13" t="n">
+        <v>-0.1111563078875181</v>
+      </c>
+      <c r="H13" t="n">
+        <v>-0.2726196665186457</v>
+      </c>
+      <c r="I13" t="n">
+        <v>0.01309623784164529</v>
+      </c>
+      <c r="J13" t="n">
+        <v>0.2099841321712681</v>
+      </c>
+      <c r="K13" t="n">
         <v>-0.006348934801478068</v>
       </c>
-      <c r="G10" t="n">
+      <c r="L13" t="n">
         <v>-0.1750732526460696</v>
       </c>
-      <c r="H10" t="n">
-        <v>0.01309623784164529</v>
-      </c>
-      <c r="I10" t="n">
-        <v>0.2099841321712681</v>
-      </c>
-      <c r="J10" t="n">
+      <c r="M13" t="n">
         <v>1</v>
       </c>
     </row>
@@ -1421,7 +1676,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>0.07875321484733945</v>
+        <v>0.07301659949693423</v>
       </c>
     </row>
   </sheetData>
